--- a/transactions.xlsx
+++ b/transactions.xlsx
@@ -1,73 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS TEST\Downloads\Slip\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52248AE-8D1D-4912-BD21-BCE74D9B81E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>amount</t>
-  </si>
-  <si>
-    <t>sender</t>
-  </si>
-  <si>
-    <t>receiver</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>bank</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -85,24 +46,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -390,58 +408,2754 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="10.19921875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sender</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>receiver</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>path</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>transaction_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>15/10/2569</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ด.ญ. ณัฐนิชา อินต๊ะราชา</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283642.jpg</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>G Wallet</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>E38948d3a5df84d6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>16/10/2569</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ ทิพย์สนิทกุล</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283642_1.jpg</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>87a9cedac0c14cbfa73aebd9df3a8014</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>19:49</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>31</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>นาย ณัฐพงษ์ ยุทธเสน</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>slips\2026-10\1283642_1.jpg</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ธ.กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>016288194955ATF09968</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>15/10/2569</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ล้านข้าวจุฬาอินเตอร์</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283642_2.jpg</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2fc0da87b7f24da8a27919772231206f</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15/10/2569</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>จันทิมา ถั่วทอง</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283642_3.jpg</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>92f38e616c22441b95bbaa7ec272bd25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศึกษากิจ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>slips\2026-10\1283643.jpg</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ธ.กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>016288183956BPP11539</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15/10/2569</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ ทิพย์สนิทกุล</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643.jpg</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7f8532cfaf3d4caaaf09d847e407612d</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>199</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HOME PRODUCT CENTER PCL.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>items</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>slips\2026-10\1283643_1.jpg</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ธ.กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>016288173334BPM06355</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15/10/2569</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>61</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>นาย วันชัย จำปาดี</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>transportation</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_1.jpg</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>G Wallet</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>EeOc203a4e8eb46d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>15/10/2569</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>จันทิมา ถั่วทอง</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>อาหาร ของหวาน เครื่องดื่ม</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_2.jpg</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>450d094bbfed4da29127452be0fd168b</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>15/10/2569</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ ทิพย์สนิทกุล</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_3.jpg</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>64e0b1007be54f4ea0f46cf75b839a1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>14/10/2569</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>75</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CU CO-OPERATIVE STORE-HOR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_4.jpg</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>G Wallet</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ea319259-1c23-4e49-b70c-eaed9c6ad833</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>14/10/2569</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ ทิพย์สนิทกุล</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_5.jpg</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>8cc670fecab546be81f95315a6737da3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>69</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศึกษากิจ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Food 14/10/69</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>slips\2026-10\1283643_2.jpg</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ธ.กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>016287130453APP11914</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>13/10/2569</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>279</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>นาย เพชรตัดเพชร มุสิกสาร</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_6.jpg</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ธ.กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>016286205724BPP03029</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>13/10/2569</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>จันทิมา ถั่วทอง</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_7.jpg</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1cef52827dc44d68b08369ae663d9cfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>13/10/2569</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ ทิพย์สนิทกุล</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_8.jpg</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ce81a082d4f74305ad30d0236a2bd8cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>13/10/2569</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>จันทิมา ถั่วทอง</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_9.jpg</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0e05ddd0a79249ecb3102b352a3c6cc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>13/10/2569</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ ทิพย์สนิทกุล</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_10.jpg</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0b58cf9b392044ce93f781de81316981</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12/10/2569</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>22:59</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>29</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DONKI (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_11.jpg</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>5ce4f94e-83da-4970-84cf-0d69f6a89e5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>54</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CU CO-OPERATIVE STORE-HOR</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>slips\2026-10\1283643_3.jpg</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>G Wallet</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>17af80a1-1760-49c7-86bd-e34df8cd585e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12/10/2569</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>18</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ล้านข้าวจุฬาอินเตอร์</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_13.jpg</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>723351a44cf648cfb62ca968872a2f18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12/10/2569</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ ทิพย์สนิทกุล</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_14.jpg</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>a11ccef2bdc7494aa46dea3a0ac2d028</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12/10/2569</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>18</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ ทิพย์สนิทกุล</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_15.jpg</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>cf669080827c4b8d85dc366a4954a8e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>12/10/2569</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>17</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศ</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VALABLE PROJECT</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Food 12/10/69</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>items</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>slips\2026-10\1283643_4.jpg</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ธ.กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>016285123601BPM11227</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12/10/2569</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ ทิพย์สนิทกุล</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_16.jpg</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>42caf25dc0744a73b9e5b9cc8eb990ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>12/10/2569</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ ทิพย์สนิทกุล</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_17.jpg</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>e9a6dbcac32542c1b215d95a86daf463</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12/10/2569</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>28</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ล้านข้าวจุฬาอินเตอร์</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_18.jpg</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>c642cf085fab42f989fd2a4a1efd0f50</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>01:35</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>110</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ทรูมันนี่</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Youtube premium 12/10/69</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>slips\2026-10\1283643_5.jpg</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>016285013520APM04870</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>00:50</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศึกษกิจ</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Food 12/10/69</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>slips\2026-10\1283643_6.jpg</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ธ.กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>016285005046BPP04362</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>200</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ทรูมันนี่</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>slips\2026-10\1283643_7.jpg</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ธ.กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>016284231915BPM19717</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>11/10/2569</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ป้าสมาน</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_19.jpg</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>b373aaffb18349169778c3f7588ecad6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>11/10/2569</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>24</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ล้านข้าวจุฬาอินเตอร์</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_20.jpg</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>3a4563e1716d48baa4827fc6d7a9f816</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>11/10/2569</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ป้าสมาน</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_21.jpg</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>469469e5a14d46c0bccb88d34108f6a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>11/10/2569</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>47</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>CU CO-OPERATIVE STORE-HOR</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_22.jpg</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>G Wallet</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>76224893-be31-4b1d-a8e8-1e8b5592432e</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>11/10/2569</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ป้าสมาน</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_23.jpg</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>d8c0262df16246fd81cdddd3a583edd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>11/10/2569</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>36</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ล้านข้าวจุฬาอินเตอร์</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_24.jpg</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1b5c62fled274c6bb0d0f54404cf504b</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>11/10/2569</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศึกษากิจ</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_25.jpg</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ธ.กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>016284122408APP08078</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>39</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>TrueMoney Shop (โรงอาหารหอพักนิสิตจุฬาฯ เบอร์4)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>slips\2026-10\1283643_8.jpg</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ธ.กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>016283195310APM10961</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10/10/2569</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ ทิพย์สนิทกุล</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_26.jpg</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>4d5ee9203afd4358aa6dfadb9c55fbc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10/10/2569</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ป้าสมาน</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>อาหาร ของหวาน เครื่องดื่ม</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_27.jpg</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>8535c16f0ab34e7cb57082ec32b95a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10/10/2569</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>32</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ล้านข้าวจุฬาอินเตอร์</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_28.jpg</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>เป๋าตัง</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>6f54049255d14f05827ac00e784a1f93</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>10/10/2569</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" s="2"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" s="2"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ ทิพย์สนิทกุล</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_29.jpg</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>f01c5192406244d2a78702756d5f934</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>10/10/2569</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศึกษ****</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศึกษ****</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>slips\2569-10\1283643_30.jpg</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>PromptPay</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>50059242706041</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>40</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>NITIKAN S</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SCB มณี SHOP (ล้านข้าวจุฬาอินเตอร์)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>slips\2026-10\1_2.jpg</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>KBank</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0462895o98t9it43QnKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศึกษากิจ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศ</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>slips\2026-10\1_3.jpg</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ธ.กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>016284122323BTF09274</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>15/10/2569</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศ***</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ ทิพย์สนิทกุล</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>G-Wallet</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>cc33886b0d7d4cdcac3fa9dd9d2d6ae4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>60</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>NITIKAN S</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SCB มณี SHOP (CENTER)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>กานตptมิว</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>KBank</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0462895o98trc6diUpPi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>นาง ฐิติญา ส</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศึกษากิจ</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>สัปดาห</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ธ.กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>016284121949BPP12843</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>17/10/2569</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2,500.00</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>นางฐิติญา ส***</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>นาย นิธิกานต์ ศึกษกิจ</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>กานต์17ตค</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>slips\2569-10\gf.jpg</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>กรุงไทย</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Ad39900b2560349ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>NITIKAN S</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>นิธิกานต์ ศึกษากิจ</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>slips\2026-10\636508659853558237.jpg</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>KBank</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0462905o9908ktobn5nP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2,100.00</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>NITIKAN S</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>NITIKAN SUKSAKIT</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>slips\2026-10\636509002444308549.jpg</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>KBank</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0462905o9908nfn3PTfa</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J8">
-    <sortCondition ref="A2:A8"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>